--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -586,19 +586,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H4" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I4" s="2">
         <v>6.3</v>
@@ -621,19 +621,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="H5" s="1">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="I5" s="2">
         <v>6.3</v>
@@ -723,19 +723,19 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E8">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>66</v>
       </c>
       <c r="G8" s="1">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="H8" s="1">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="I8" s="2">
         <v>6.2</v>
@@ -793,19 +793,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H10" s="1">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="I10" s="2">
         <v>6.9</v>
@@ -828,22 +828,22 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -898,28 +898,28 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>72.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>27.8</v>
+        <v>31.6</v>
       </c>
       <c r="I13" s="2">
         <v>7.2</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -930,28 +930,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
-        <v>83.5</v>
+        <v>82.8</v>
       </c>
       <c r="H14" s="1">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -959,28 +959,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>269</v>
       </c>
       <c r="F15">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="I15" s="2">
         <v>6.5</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
@@ -1115,13 +1115,13 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="1">
         <v>100</v>
@@ -1150,13 +1150,13 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="1">
         <v>100</v>
@@ -1252,13 +1252,13 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K8" s="1">
         <v>100</v>
@@ -1322,13 +1322,13 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K10" s="1">
         <v>100</v>
@@ -1357,13 +1357,13 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K11" s="1">
         <v>100</v>
@@ -1427,13 +1427,13 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K13" s="1">
         <v>100</v>
@@ -1459,13 +1459,13 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K14" s="1">
         <v>100</v>
@@ -1488,13 +1488,13 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K15" s="1">
         <v>100</v>
@@ -1644,19 +1644,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4">
         <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="H4" s="1">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="I4" s="2">
         <v>6.3</v>
@@ -1679,19 +1679,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>9</v>
       </c>
       <c r="G5" s="1">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="H5" s="1">
-        <v>23.1</v>
+        <v>22.5</v>
       </c>
       <c r="I5" s="2">
         <v>6.4</v>
@@ -1781,19 +1781,19 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E8">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>66</v>
       </c>
       <c r="G8" s="1">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="H8" s="1">
-        <v>34.2</v>
+        <v>33.8</v>
       </c>
       <c r="I8" s="2">
         <v>6.2</v>
@@ -1851,19 +1851,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>76.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="H10" s="1">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="I10" s="2">
         <v>6.9</v>
@@ -1886,22 +1886,22 @@
         <v>24</v>
       </c>
       <c r="D11">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>82.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="I11" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1956,28 +1956,28 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
         <v>13</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>72.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>27.8</v>
+        <v>31.6</v>
       </c>
       <c r="I13" s="2">
         <v>7.2</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>0</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1988,28 +1988,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1">
-        <v>83.5</v>
+        <v>82.8</v>
       </c>
       <c r="H14" s="1">
-        <v>16.5</v>
+        <v>17.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2017,28 +2017,28 @@
         <v>15</v>
       </c>
       <c r="D15">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15">
         <v>269</v>
       </c>
       <c r="F15">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" s="1">
-        <v>74.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="I15" s="2">
         <v>6.5</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -586,19 +586,19 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>9</v>
       </c>
       <c r="G4" s="1">
-        <v>74.3</v>
+        <v>73.5</v>
       </c>
       <c r="H4" s="1">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="I4" s="2">
         <v>6.3</v>
@@ -723,19 +723,19 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F8">
         <v>66</v>
       </c>
       <c r="G8" s="1">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="H8" s="1">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="I8" s="2">
         <v>6.2</v>
@@ -793,19 +793,19 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>76.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="I10" s="2">
         <v>6.9</v>
@@ -913,13 +913,13 @@
         <v>31.6</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -930,28 +930,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E14">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F14">
         <v>29</v>
       </c>
       <c r="G14" s="1">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="I14" s="2">
         <v>6.8</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -977,10 +977,10 @@
         <v>6.5</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1048,25 +1048,25 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>55.6</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1083,25 +1083,25 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>41.7</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1115,28 +1115,28 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>17.9</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1223,25 +1223,25 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>36.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1252,28 +1252,28 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="F8">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>28.4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1322,28 +1322,28 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>75.7</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>24.3</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1430,25 +1430,25 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>21.1</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1459,28 +1459,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F14">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>62.9</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>37.1</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="J14">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="F15">
-        <v>364</v>
+        <v>118</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>32.4</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
-        <v>364</v>
+        <v>39</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>
@@ -1577,19 +1577,19 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>70.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="H2" s="1">
-        <v>29.6</v>
+        <v>44.4</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1612,19 +1612,19 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="H3" s="1">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I3" s="2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1644,22 +1644,22 @@
         <v>18</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>74.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>25.7</v>
+        <v>20.6</v>
       </c>
       <c r="I4" s="2">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1682,19 +1682,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="H5" s="1">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="I5" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1">
-        <v>66.7</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>33.3</v>
+        <v>17.9</v>
       </c>
       <c r="I6" s="2">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>50</v>
+        <v>63.3</v>
       </c>
       <c r="H7" s="1">
-        <v>50</v>
+        <v>36.7</v>
       </c>
       <c r="I7" s="2">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1781,22 +1781,22 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E8">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F8">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G8" s="1">
-        <v>66.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>33.8</v>
+        <v>28.4</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I9" s="2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1851,22 +1851,22 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>76.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>23.7</v>
+        <v>5.1</v>
       </c>
       <c r="I10" s="2">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="1">
-        <v>81.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="H12" s="1">
-        <v>18.9</v>
+        <v>24.3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1959,25 +1959,25 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>68.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>31.6</v>
+        <v>21.1</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1988,28 +1988,28 @@
         <v>14</v>
       </c>
       <c r="D14">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E14">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G14" s="1">
-        <v>82.8</v>
+        <v>81.8</v>
       </c>
       <c r="H14" s="1">
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
       <c r="I14" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2020,25 +2020,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F15">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G15" s="1">
-        <v>73.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>26.1</v>
+        <v>23.6</v>
       </c>
       <c r="I15" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -1360,25 +1360,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>25.6</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>170</v>
       </c>
       <c r="E14">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
-        <v>62.9</v>
+        <v>80</v>
       </c>
       <c r="H14" s="1">
-        <v>37.1</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="J14">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>22.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="F15">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G15" s="1">
-        <v>67.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="H15" s="1">
-        <v>32.4</v>
+        <v>24.5</v>
       </c>
       <c r="I15" s="2">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1889,16 +1889,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
-        <v>82.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>17.9</v>
+        <v>25.6</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>
@@ -1991,16 +1991,16 @@
         <v>170</v>
       </c>
       <c r="E14">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G14" s="1">
-        <v>81.8</v>
+        <v>80</v>
       </c>
       <c r="H14" s="1">
-        <v>18.2</v>
+        <v>20</v>
       </c>
       <c r="I14" s="2">
         <v>6.9</v>
@@ -2020,16 +2020,16 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F15">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G15" s="1">
-        <v>76.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="H15" s="1">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="I15" s="2">
         <v>6.8</v>

--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -1577,16 +1577,16 @@
         <v>27</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1">
-        <v>55.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>44.4</v>
+        <v>29.6</v>
       </c>
       <c r="I2" s="2">
         <v>6.3</v>
@@ -1612,16 +1612,16 @@
         <v>24</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>58.3</v>
+        <v>70.8</v>
       </c>
       <c r="H3" s="1">
-        <v>41.7</v>
+        <v>29.2</v>
       </c>
       <c r="I3" s="2">
         <v>6.3</v>
@@ -1647,19 +1647,19 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1">
-        <v>79.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>20.6</v>
+        <v>17.6</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1682,16 +1682,16 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G5" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I5" s="2">
         <v>6.7</v>
@@ -1717,19 +1717,19 @@
         <v>39</v>
       </c>
       <c r="E6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>82.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>17.9</v>
+        <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>63.3</v>
+        <v>90</v>
       </c>
       <c r="H7" s="1">
-        <v>36.7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1784,16 +1784,16 @@
         <v>194</v>
       </c>
       <c r="E8">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="F8">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G8" s="1">
-        <v>71.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="H8" s="1">
-        <v>28.4</v>
+        <v>17.5</v>
       </c>
       <c r="I8" s="2">
         <v>6.7</v>
@@ -1819,19 +1819,19 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="H9" s="1">
-        <v>25</v>
+        <v>16.7</v>
       </c>
       <c r="I9" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>5.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1889,16 +1889,16 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>74.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>25.6</v>
+        <v>15.4</v>
       </c>
       <c r="I11" s="2">
         <v>6.7</v>
@@ -1924,19 +1924,19 @@
         <v>37</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>75.7</v>
+        <v>73</v>
       </c>
       <c r="H12" s="1">
-        <v>24.3</v>
+        <v>27</v>
       </c>
       <c r="I12" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>170</v>
       </c>
       <c r="E14">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G14" s="1">
-        <v>80</v>
+        <v>83.5</v>
       </c>
       <c r="H14" s="1">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="I14" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>364</v>
       </c>
       <c r="E15">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="F15">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1">
-        <v>75.5</v>
+        <v>83</v>
       </c>
       <c r="H15" s="1">
-        <v>24.5</v>
+        <v>17</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -1589,7 +1589,7 @@
         <v>29.6</v>
       </c>
       <c r="I2" s="2">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>29.2</v>
       </c>
       <c r="I3" s="2">
-        <v>6.3</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>17.6</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="I5" s="2">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>6.7</v>
+        <v>9.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>17.5</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>16.7</v>
       </c>
       <c r="I9" s="2">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>5.1</v>
       </c>
       <c r="I10" s="2">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>15.4</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>27</v>
       </c>
       <c r="I12" s="2">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>21.1</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>16.5</v>
       </c>
       <c r="I14" s="2">
-        <v>6.8</v>
+        <v>9.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>17</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Cultura Digital - Estadisticos 20231.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20231.xlsx
@@ -1589,7 +1589,7 @@
         <v>29.6</v>
       </c>
       <c r="I2" s="2">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>29.2</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>6.3</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1659,7 +1659,7 @@
         <v>17.6</v>
       </c>
       <c r="I4" s="2">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="I5" s="2">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>15.4</v>
       </c>
       <c r="I6" s="2">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>10</v>
       </c>
       <c r="I7" s="2">
-        <v>9.5</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>17.5</v>
       </c>
       <c r="I8" s="2">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v>16.7</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>5.1</v>
       </c>
       <c r="I10" s="2">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1901,7 +1901,7 @@
         <v>15.4</v>
       </c>
       <c r="I11" s="2">
-        <v>9.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>27</v>
       </c>
       <c r="I12" s="2">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>21.1</v>
       </c>
       <c r="I13" s="2">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2003,7 +2003,7 @@
         <v>16.5</v>
       </c>
       <c r="I14" s="2">
-        <v>9.1</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2032,7 +2032,7 @@
         <v>17</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
